--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.52896683527198</v>
+        <v>4.960957110731696</v>
       </c>
       <c r="D2" t="n">
-        <v>30.24651285244529</v>
+        <v>4.915058338522361</v>
       </c>
       <c r="E2" t="n">
-        <v>20.59866687625186</v>
+        <v>3.347283367390927</v>
       </c>
       <c r="F2" t="n">
-        <v>10.70609221729576</v>
+        <v>1.739739985310561</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.5324211100297</v>
+        <v>5.124018430379826</v>
       </c>
       <c r="D3" t="n">
-        <v>31.37838484937948</v>
+        <v>5.098987538024165</v>
       </c>
       <c r="E3" t="n">
-        <v>20.59866687625186</v>
+        <v>3.347283367390927</v>
       </c>
       <c r="F3" t="n">
-        <v>10.70609221729576</v>
+        <v>1.739739985310561</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.71842287326356</v>
+        <v>12.14174371690533</v>
       </c>
       <c r="D4" t="n">
-        <v>53.50233639758174</v>
+        <v>8.694129664607033</v>
       </c>
       <c r="E4" t="n">
-        <v>20.59866687625186</v>
+        <v>3.347283367390927</v>
       </c>
       <c r="F4" t="n">
-        <v>10.70609221729576</v>
+        <v>1.739739985310561</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
